--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG136"/>
+  <dimension ref="A1:AG137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14493,6 +14493,109 @@
       </c>
       <c r="AG136" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1506900</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F137" t="n">
+        <v>12344</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>25330</v>
+      </c>
+      <c r="I137" t="n">
+        <v>8</v>
+      </c>
+      <c r="J137" t="n">
+        <v>49678</v>
+      </c>
+      <c r="K137" t="n">
+        <v>77</v>
+      </c>
+      <c r="L137" t="n">
+        <v>2120</v>
+      </c>
+      <c r="M137" t="n">
+        <v>5</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1635</v>
+      </c>
+      <c r="O137" t="n">
+        <v>2</v>
+      </c>
+      <c r="P137" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>356</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>514317</v>
+      </c>
+      <c r="U137" t="n">
+        <v>2142</v>
+      </c>
+      <c r="V137" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>148259</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>410</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>4681</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>2603</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG137"/>
+  <dimension ref="A1:AG138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14596,6 +14596,109 @@
       </c>
       <c r="AG137" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1664</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1508600</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F138" t="n">
+        <v>12345</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>25331</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>49752</v>
+      </c>
+      <c r="K138" t="n">
+        <v>74</v>
+      </c>
+      <c r="L138" t="n">
+        <v>2127</v>
+      </c>
+      <c r="M138" t="n">
+        <v>7</v>
+      </c>
+      <c r="N138" t="n">
+        <v>1637</v>
+      </c>
+      <c r="O138" t="n">
+        <v>2</v>
+      </c>
+      <c r="P138" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>356</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>516441</v>
+      </c>
+      <c r="U138" t="n">
+        <v>2124</v>
+      </c>
+      <c r="V138" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>148807</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>548</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>4683</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>2615</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG138"/>
+  <dimension ref="A1:AG139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14699,6 +14699,109 @@
       </c>
       <c r="AG138" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1665</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F139" t="n">
+        <v>12345</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>25334</v>
+      </c>
+      <c r="I139" t="n">
+        <v>3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>49793</v>
+      </c>
+      <c r="K139" t="n">
+        <v>41</v>
+      </c>
+      <c r="L139" t="n">
+        <v>2131</v>
+      </c>
+      <c r="M139" t="n">
+        <v>4</v>
+      </c>
+      <c r="N139" t="n">
+        <v>1638</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>356</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>518280</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1839</v>
+      </c>
+      <c r="V139" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>149183</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>376</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>4690</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>2626</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG139"/>
+  <dimension ref="A1:AG140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14802,6 +14802,109 @@
       </c>
       <c r="AG139" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1666</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1511530</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1530</v>
+      </c>
+      <c r="F140" t="n">
+        <v>12345</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>25339</v>
+      </c>
+      <c r="I140" t="n">
+        <v>5</v>
+      </c>
+      <c r="J140" t="n">
+        <v>49820</v>
+      </c>
+      <c r="K140" t="n">
+        <v>27</v>
+      </c>
+      <c r="L140" t="n">
+        <v>2132</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1642</v>
+      </c>
+      <c r="O140" t="n">
+        <v>4</v>
+      </c>
+      <c r="P140" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>356</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>519069</v>
+      </c>
+      <c r="U140" t="n">
+        <v>789</v>
+      </c>
+      <c r="V140" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>149557</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>374</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>4692</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>2630</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG140"/>
+  <dimension ref="A1:AG141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14905,6 +14905,109 @@
       </c>
       <c r="AG140" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1667</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1513490</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F141" t="n">
+        <v>12346</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>25345</v>
+      </c>
+      <c r="I141" t="n">
+        <v>6</v>
+      </c>
+      <c r="J141" t="n">
+        <v>49863</v>
+      </c>
+      <c r="K141" t="n">
+        <v>43</v>
+      </c>
+      <c r="L141" t="n">
+        <v>2139</v>
+      </c>
+      <c r="M141" t="n">
+        <v>7</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1645</v>
+      </c>
+      <c r="O141" t="n">
+        <v>3</v>
+      </c>
+      <c r="P141" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>356</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>520508</v>
+      </c>
+      <c r="U141" t="n">
+        <v>1439</v>
+      </c>
+      <c r="V141" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>150018</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>461</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>4697</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>2644</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG141"/>
+  <dimension ref="A1:AG142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15008,6 +15008,109 @@
       </c>
       <c r="AG141" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1514910</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F142" t="n">
+        <v>12351</v>
+      </c>
+      <c r="G142" t="n">
+        <v>5</v>
+      </c>
+      <c r="H142" t="n">
+        <v>25352</v>
+      </c>
+      <c r="I142" t="n">
+        <v>7</v>
+      </c>
+      <c r="J142" t="n">
+        <v>49938</v>
+      </c>
+      <c r="K142" t="n">
+        <v>75</v>
+      </c>
+      <c r="L142" t="n">
+        <v>2142</v>
+      </c>
+      <c r="M142" t="n">
+        <v>3</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1646</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>356</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>522316</v>
+      </c>
+      <c r="U142" t="n">
+        <v>1808</v>
+      </c>
+      <c r="V142" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>150442</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>424</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>4701</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>2656</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG142"/>
+  <dimension ref="A1:AG143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15111,6 +15111,109 @@
       </c>
       <c r="AG142" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1669</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1516430</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F143" t="n">
+        <v>12352</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>25357</v>
+      </c>
+      <c r="I143" t="n">
+        <v>5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>50011</v>
+      </c>
+      <c r="K143" t="n">
+        <v>73</v>
+      </c>
+      <c r="L143" t="n">
+        <v>2143</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1657</v>
+      </c>
+      <c r="O143" t="n">
+        <v>11</v>
+      </c>
+      <c r="P143" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>356</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>524132</v>
+      </c>
+      <c r="U143" t="n">
+        <v>1816</v>
+      </c>
+      <c r="V143" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>150922</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>480</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>4703</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>2672</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG143"/>
+  <dimension ref="A1:AG144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15214,6 +15214,109 @@
       </c>
       <c r="AG143" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1670</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1517990</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F144" t="n">
+        <v>12356</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4</v>
+      </c>
+      <c r="H144" t="n">
+        <v>25361</v>
+      </c>
+      <c r="I144" t="n">
+        <v>4</v>
+      </c>
+      <c r="J144" t="n">
+        <v>50067</v>
+      </c>
+      <c r="K144" t="n">
+        <v>56</v>
+      </c>
+      <c r="L144" t="n">
+        <v>2146</v>
+      </c>
+      <c r="M144" t="n">
+        <v>3</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1659</v>
+      </c>
+      <c r="O144" t="n">
+        <v>2</v>
+      </c>
+      <c r="P144" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>356</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>525965</v>
+      </c>
+      <c r="U144" t="n">
+        <v>1833</v>
+      </c>
+      <c r="V144" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>151345</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>423</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>4716</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>2695</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG144"/>
+  <dimension ref="A1:AG145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15317,6 +15317,109 @@
       </c>
       <c r="AG144" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1671</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1519650</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1660</v>
+      </c>
+      <c r="F145" t="n">
+        <v>12361</v>
+      </c>
+      <c r="G145" t="n">
+        <v>5</v>
+      </c>
+      <c r="H145" t="n">
+        <v>25365</v>
+      </c>
+      <c r="I145" t="n">
+        <v>4</v>
+      </c>
+      <c r="J145" t="n">
+        <v>50142</v>
+      </c>
+      <c r="K145" t="n">
+        <v>75</v>
+      </c>
+      <c r="L145" t="n">
+        <v>2149</v>
+      </c>
+      <c r="M145" t="n">
+        <v>3</v>
+      </c>
+      <c r="N145" t="n">
+        <v>1662</v>
+      </c>
+      <c r="O145" t="n">
+        <v>3</v>
+      </c>
+      <c r="P145" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>356</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>527693</v>
+      </c>
+      <c r="U145" t="n">
+        <v>1728</v>
+      </c>
+      <c r="V145" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>151861</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>516</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>4729</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>2712</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG145"/>
+  <dimension ref="A1:AG146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15420,6 +15420,109 @@
       </c>
       <c r="AG145" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1672</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1520880</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F146" t="n">
+        <v>12364</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="n">
+        <v>25374</v>
+      </c>
+      <c r="I146" t="n">
+        <v>9</v>
+      </c>
+      <c r="J146" t="n">
+        <v>50184</v>
+      </c>
+      <c r="K146" t="n">
+        <v>42</v>
+      </c>
+      <c r="L146" t="n">
+        <v>2151</v>
+      </c>
+      <c r="M146" t="n">
+        <v>2</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1663</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>356</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>529134</v>
+      </c>
+      <c r="U146" t="n">
+        <v>1441</v>
+      </c>
+      <c r="V146" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>152173</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>312</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>4733</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>2720</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG146"/>
+  <dimension ref="A1:AG147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15523,6 +15523,109 @@
       </c>
       <c r="AG146" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1673</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1522440</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F147" t="n">
+        <v>12367</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>25387</v>
+      </c>
+      <c r="I147" t="n">
+        <v>13</v>
+      </c>
+      <c r="J147" t="n">
+        <v>50216</v>
+      </c>
+      <c r="K147" t="n">
+        <v>32</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2152</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1665</v>
+      </c>
+      <c r="O147" t="n">
+        <v>2</v>
+      </c>
+      <c r="P147" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>356</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>530560</v>
+      </c>
+      <c r="U147" t="n">
+        <v>1426</v>
+      </c>
+      <c r="V147" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>152553</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>380</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>4737</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2723</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG147"/>
+  <dimension ref="A1:AG148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15626,6 +15626,109 @@
       </c>
       <c r="AG147" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1674</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1523980</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F148" t="n">
+        <v>12367</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>25402</v>
+      </c>
+      <c r="I148" t="n">
+        <v>15</v>
+      </c>
+      <c r="J148" t="n">
+        <v>50240</v>
+      </c>
+      <c r="K148" t="n">
+        <v>24</v>
+      </c>
+      <c r="L148" t="n">
+        <v>2154</v>
+      </c>
+      <c r="M148" t="n">
+        <v>2</v>
+      </c>
+      <c r="N148" t="n">
+        <v>1669</v>
+      </c>
+      <c r="O148" t="n">
+        <v>4</v>
+      </c>
+      <c r="P148" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>1</v>
+      </c>
+      <c r="R148" t="n">
+        <v>356</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>531352</v>
+      </c>
+      <c r="U148" t="n">
+        <v>792</v>
+      </c>
+      <c r="V148" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>152782</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>229</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>4740</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>2727</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG148"/>
+  <dimension ref="A1:AG149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15729,6 +15729,109 @@
       </c>
       <c r="AG148" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1675</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1525570</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F149" t="n">
+        <v>12369</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>25415</v>
+      </c>
+      <c r="I149" t="n">
+        <v>13</v>
+      </c>
+      <c r="J149" t="n">
+        <v>50275</v>
+      </c>
+      <c r="K149" t="n">
+        <v>35</v>
+      </c>
+      <c r="L149" t="n">
+        <v>2157</v>
+      </c>
+      <c r="M149" t="n">
+        <v>3</v>
+      </c>
+      <c r="N149" t="n">
+        <v>1669</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>356</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>532575</v>
+      </c>
+      <c r="U149" t="n">
+        <v>1223</v>
+      </c>
+      <c r="V149" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>153152</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>370</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>4741</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2736</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG149"/>
+  <dimension ref="A1:AG150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15832,6 +15832,109 @@
       </c>
       <c r="AG149" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1676</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1527280</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F150" t="n">
+        <v>12376</v>
+      </c>
+      <c r="G150" t="n">
+        <v>7</v>
+      </c>
+      <c r="H150" t="n">
+        <v>25435</v>
+      </c>
+      <c r="I150" t="n">
+        <v>20</v>
+      </c>
+      <c r="J150" t="n">
+        <v>50371</v>
+      </c>
+      <c r="K150" t="n">
+        <v>96</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2160</v>
+      </c>
+      <c r="M150" t="n">
+        <v>3</v>
+      </c>
+      <c r="N150" t="n">
+        <v>1673</v>
+      </c>
+      <c r="O150" t="n">
+        <v>4</v>
+      </c>
+      <c r="P150" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>356</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>534020</v>
+      </c>
+      <c r="U150" t="n">
+        <v>1445</v>
+      </c>
+      <c r="V150" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>153728</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>576</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>4749</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>2748</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG150"/>
+  <dimension ref="A1:AG151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15935,6 +15935,109 @@
       </c>
       <c r="AG150" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1677</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1528970</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1690</v>
+      </c>
+      <c r="F151" t="n">
+        <v>12384</v>
+      </c>
+      <c r="G151" t="n">
+        <v>8</v>
+      </c>
+      <c r="H151" t="n">
+        <v>25442</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>50428</v>
+      </c>
+      <c r="K151" t="n">
+        <v>57</v>
+      </c>
+      <c r="L151" t="n">
+        <v>2163</v>
+      </c>
+      <c r="M151" t="n">
+        <v>3</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1677</v>
+      </c>
+      <c r="O151" t="n">
+        <v>4</v>
+      </c>
+      <c r="P151" t="n">
+        <v>444</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>1</v>
+      </c>
+      <c r="R151" t="n">
+        <v>356</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>535846</v>
+      </c>
+      <c r="U151" t="n">
+        <v>1826</v>
+      </c>
+      <c r="V151" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>154245</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>517</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>4756</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>2762</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG151"/>
+  <dimension ref="A1:AG163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16038,6 +16038,1242 @@
       </c>
       <c r="AG151" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1678</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1531060</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2090</v>
+      </c>
+      <c r="F152" t="n">
+        <v>12385</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>25450</v>
+      </c>
+      <c r="I152" t="n">
+        <v>8</v>
+      </c>
+      <c r="J152" t="n">
+        <v>50477</v>
+      </c>
+      <c r="K152" t="n">
+        <v>49</v>
+      </c>
+      <c r="L152" t="n">
+        <v>2165</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
+      <c r="N152" t="n">
+        <v>1679</v>
+      </c>
+      <c r="O152" t="n">
+        <v>2</v>
+      </c>
+      <c r="P152" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>356</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>537228</v>
+      </c>
+      <c r="U152" t="n">
+        <v>1382</v>
+      </c>
+      <c r="V152" t="n">
+        <v>5118</v>
+      </c>
+      <c r="W152" t="n">
+        <v>168</v>
+      </c>
+      <c r="X152" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>154735</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>490</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>4763</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>2774</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1679</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1532500</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F153" t="n">
+        <v>12388</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3</v>
+      </c>
+      <c r="H153" t="n">
+        <v>25463</v>
+      </c>
+      <c r="I153" t="n">
+        <v>13</v>
+      </c>
+      <c r="J153" t="n">
+        <v>50498</v>
+      </c>
+      <c r="K153" t="n">
+        <v>21</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2169</v>
+      </c>
+      <c r="M153" t="n">
+        <v>4</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1681</v>
+      </c>
+      <c r="O153" t="n">
+        <v>2</v>
+      </c>
+      <c r="P153" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>356</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>538702</v>
+      </c>
+      <c r="U153" t="n">
+        <v>1474</v>
+      </c>
+      <c r="V153" t="n">
+        <v>5118</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>155031</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>296</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>4765</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1533970</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F154" t="n">
+        <v>12388</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>25463</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>50519</v>
+      </c>
+      <c r="K154" t="n">
+        <v>21</v>
+      </c>
+      <c r="L154" t="n">
+        <v>2171</v>
+      </c>
+      <c r="M154" t="n">
+        <v>2</v>
+      </c>
+      <c r="N154" t="n">
+        <v>1682</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>356</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>540095</v>
+      </c>
+      <c r="U154" t="n">
+        <v>1393</v>
+      </c>
+      <c r="V154" t="n">
+        <v>5121</v>
+      </c>
+      <c r="W154" t="n">
+        <v>3</v>
+      </c>
+      <c r="X154" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>155363</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>332</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>4770</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2789</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1681</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1535870</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F155" t="n">
+        <v>12388</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>25464</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>50555</v>
+      </c>
+      <c r="K155" t="n">
+        <v>36</v>
+      </c>
+      <c r="L155" t="n">
+        <v>2174</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1683</v>
+      </c>
+      <c r="O155" t="n">
+        <v>1</v>
+      </c>
+      <c r="P155" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>356</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>541383</v>
+      </c>
+      <c r="U155" t="n">
+        <v>1288</v>
+      </c>
+      <c r="V155" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W155" t="n">
+        <v>5</v>
+      </c>
+      <c r="X155" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>155887</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>524</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>4774</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>2803</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1682</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1537390</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F156" t="n">
+        <v>12388</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>25471</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>50592</v>
+      </c>
+      <c r="K156" t="n">
+        <v>37</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2175</v>
+      </c>
+      <c r="M156" t="n">
+        <v>1</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1683</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>356</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>542853</v>
+      </c>
+      <c r="U156" t="n">
+        <v>1470</v>
+      </c>
+      <c r="V156" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>156309</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>422</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>4780</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>2810</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1683</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1538950</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F157" t="n">
+        <v>12391</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3</v>
+      </c>
+      <c r="H157" t="n">
+        <v>25477</v>
+      </c>
+      <c r="I157" t="n">
+        <v>6</v>
+      </c>
+      <c r="J157" t="n">
+        <v>50637</v>
+      </c>
+      <c r="K157" t="n">
+        <v>45</v>
+      </c>
+      <c r="L157" t="n">
+        <v>2178</v>
+      </c>
+      <c r="M157" t="n">
+        <v>3</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1683</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>356</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>544498</v>
+      </c>
+      <c r="U157" t="n">
+        <v>1645</v>
+      </c>
+      <c r="V157" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>156731</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>422</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>4783</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>2824</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1684</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1540700</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F158" t="n">
+        <v>12391</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>25483</v>
+      </c>
+      <c r="I158" t="n">
+        <v>6</v>
+      </c>
+      <c r="J158" t="n">
+        <v>50686</v>
+      </c>
+      <c r="K158" t="n">
+        <v>49</v>
+      </c>
+      <c r="L158" t="n">
+        <v>2179</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1686</v>
+      </c>
+      <c r="O158" t="n">
+        <v>3</v>
+      </c>
+      <c r="P158" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>356</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>546240</v>
+      </c>
+      <c r="U158" t="n">
+        <v>1742</v>
+      </c>
+      <c r="V158" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>157258</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>527</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>4788</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>2837</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1685</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1542720</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F159" t="n">
+        <v>12393</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="n">
+        <v>25487</v>
+      </c>
+      <c r="I159" t="n">
+        <v>4</v>
+      </c>
+      <c r="J159" t="n">
+        <v>50733</v>
+      </c>
+      <c r="K159" t="n">
+        <v>47</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2182</v>
+      </c>
+      <c r="M159" t="n">
+        <v>3</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1688</v>
+      </c>
+      <c r="O159" t="n">
+        <v>2</v>
+      </c>
+      <c r="P159" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>356</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>548095</v>
+      </c>
+      <c r="U159" t="n">
+        <v>1855</v>
+      </c>
+      <c r="V159" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>157985</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>727</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>4793</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>2859</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1686</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1544260</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F160" t="n">
+        <v>12396</v>
+      </c>
+      <c r="G160" t="n">
+        <v>3</v>
+      </c>
+      <c r="H160" t="n">
+        <v>25494</v>
+      </c>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" t="n">
+        <v>50785</v>
+      </c>
+      <c r="K160" t="n">
+        <v>52</v>
+      </c>
+      <c r="L160" t="n">
+        <v>2184</v>
+      </c>
+      <c r="M160" t="n">
+        <v>2</v>
+      </c>
+      <c r="N160" t="n">
+        <v>1688</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>356</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>549986</v>
+      </c>
+      <c r="U160" t="n">
+        <v>1891</v>
+      </c>
+      <c r="V160" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>158551</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>566</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>4795</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>2866</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1687</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1545950</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1690</v>
+      </c>
+      <c r="F161" t="n">
+        <v>12396</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>25498</v>
+      </c>
+      <c r="I161" t="n">
+        <v>4</v>
+      </c>
+      <c r="J161" t="n">
+        <v>50836</v>
+      </c>
+      <c r="K161" t="n">
+        <v>51</v>
+      </c>
+      <c r="L161" t="n">
+        <v>2192</v>
+      </c>
+      <c r="M161" t="n">
+        <v>8</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1690</v>
+      </c>
+      <c r="O161" t="n">
+        <v>2</v>
+      </c>
+      <c r="P161" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>356</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>551876</v>
+      </c>
+      <c r="U161" t="n">
+        <v>1890</v>
+      </c>
+      <c r="V161" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>159128</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>577</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>2878</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1688</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1547780</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1830</v>
+      </c>
+      <c r="F162" t="n">
+        <v>12399</v>
+      </c>
+      <c r="G162" t="n">
+        <v>3</v>
+      </c>
+      <c r="H162" t="n">
+        <v>25502</v>
+      </c>
+      <c r="I162" t="n">
+        <v>4</v>
+      </c>
+      <c r="J162" t="n">
+        <v>50883</v>
+      </c>
+      <c r="K162" t="n">
+        <v>47</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2194</v>
+      </c>
+      <c r="M162" t="n">
+        <v>2</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1692</v>
+      </c>
+      <c r="O162" t="n">
+        <v>2</v>
+      </c>
+      <c r="P162" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>356</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>553578</v>
+      </c>
+      <c r="U162" t="n">
+        <v>1702</v>
+      </c>
+      <c r="V162" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>159795</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>667</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>4806</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>2890</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1689</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1549490</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F163" t="n">
+        <v>12402</v>
+      </c>
+      <c r="G163" t="n">
+        <v>3</v>
+      </c>
+      <c r="H163" t="n">
+        <v>25509</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>50950</v>
+      </c>
+      <c r="K163" t="n">
+        <v>67</v>
+      </c>
+      <c r="L163" t="n">
+        <v>2199</v>
+      </c>
+      <c r="M163" t="n">
+        <v>5</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1693</v>
+      </c>
+      <c r="O163" t="n">
+        <v>1</v>
+      </c>
+      <c r="P163" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>356</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>555335</v>
+      </c>
+      <c r="U163" t="n">
+        <v>1757</v>
+      </c>
+      <c r="V163" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>160412</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>617</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>4810</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>2908</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG163"/>
+  <dimension ref="A1:AG164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17274,6 +17274,109 @@
       </c>
       <c r="AG163" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1690</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1550910</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F164" t="n">
+        <v>12406</v>
+      </c>
+      <c r="G164" t="n">
+        <v>4</v>
+      </c>
+      <c r="H164" t="n">
+        <v>25515</v>
+      </c>
+      <c r="I164" t="n">
+        <v>6</v>
+      </c>
+      <c r="J164" t="n">
+        <v>51000</v>
+      </c>
+      <c r="K164" t="n">
+        <v>50</v>
+      </c>
+      <c r="L164" t="n">
+        <v>2201</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1699</v>
+      </c>
+      <c r="O164" t="n">
+        <v>6</v>
+      </c>
+      <c r="P164" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>356</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>556926</v>
+      </c>
+      <c r="U164" t="n">
+        <v>1591</v>
+      </c>
+      <c r="V164" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>160946</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>534</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>4812</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>2917</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG164"/>
+  <dimension ref="A1:AG165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17377,6 +17377,109 @@
       </c>
       <c r="AG164" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1691</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1552840</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1930</v>
+      </c>
+      <c r="F165" t="n">
+        <v>12408</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="n">
+        <v>25521</v>
+      </c>
+      <c r="I165" t="n">
+        <v>6</v>
+      </c>
+      <c r="J165" t="n">
+        <v>51039</v>
+      </c>
+      <c r="K165" t="n">
+        <v>39</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2205</v>
+      </c>
+      <c r="M165" t="n">
+        <v>4</v>
+      </c>
+      <c r="N165" t="n">
+        <v>1701</v>
+      </c>
+      <c r="O165" t="n">
+        <v>2</v>
+      </c>
+      <c r="P165" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>356</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>558457</v>
+      </c>
+      <c r="U165" t="n">
+        <v>1531</v>
+      </c>
+      <c r="V165" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W165" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>161503</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>557</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>4815</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>2924</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG165"/>
+  <dimension ref="A1:AG166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17480,6 +17480,109 @@
       </c>
       <c r="AG165" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1692</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1554310</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F166" t="n">
+        <v>12410</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="n">
+        <v>25527</v>
+      </c>
+      <c r="I166" t="n">
+        <v>6</v>
+      </c>
+      <c r="J166" t="n">
+        <v>51090</v>
+      </c>
+      <c r="K166" t="n">
+        <v>51</v>
+      </c>
+      <c r="L166" t="n">
+        <v>2209</v>
+      </c>
+      <c r="M166" t="n">
+        <v>4</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1703</v>
+      </c>
+      <c r="O166" t="n">
+        <v>2</v>
+      </c>
+      <c r="P166" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>356</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>559873</v>
+      </c>
+      <c r="U166" t="n">
+        <v>1416</v>
+      </c>
+      <c r="V166" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>162056</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>553</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>4818</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>2927</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG166"/>
+  <dimension ref="A1:AG167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17583,6 +17583,109 @@
       </c>
       <c r="AG166" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1693</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1555700</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F167" t="n">
+        <v>12412</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="n">
+        <v>25534</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>51141</v>
+      </c>
+      <c r="K167" t="n">
+        <v>51</v>
+      </c>
+      <c r="L167" t="n">
+        <v>2211</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1704</v>
+      </c>
+      <c r="O167" t="n">
+        <v>1</v>
+      </c>
+      <c r="P167" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>356</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>561762</v>
+      </c>
+      <c r="U167" t="n">
+        <v>1889</v>
+      </c>
+      <c r="V167" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>162418</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>362</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>4823</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>2942</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG167"/>
+  <dimension ref="A1:AG168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17686,6 +17686,109 @@
       </c>
       <c r="AG167" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1694</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1557350</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F168" t="n">
+        <v>12414</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>25535</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>51195</v>
+      </c>
+      <c r="K168" t="n">
+        <v>54</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2212</v>
+      </c>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1704</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>356</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>563589</v>
+      </c>
+      <c r="U168" t="n">
+        <v>1827</v>
+      </c>
+      <c r="V168" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W168" t="n">
+        <v>0</v>
+      </c>
+      <c r="X168" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>162789</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>371</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>4828</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2951</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG168"/>
+  <dimension ref="A1:AG169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17789,6 +17789,109 @@
       </c>
       <c r="AG168" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1695</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1559230</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F169" t="n">
+        <v>12414</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>25537</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2</v>
+      </c>
+      <c r="J169" t="n">
+        <v>51233</v>
+      </c>
+      <c r="K169" t="n">
+        <v>38</v>
+      </c>
+      <c r="L169" t="n">
+        <v>2216</v>
+      </c>
+      <c r="M169" t="n">
+        <v>4</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1707</v>
+      </c>
+      <c r="O169" t="n">
+        <v>3</v>
+      </c>
+      <c r="P169" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>356</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>564897</v>
+      </c>
+      <c r="U169" t="n">
+        <v>1308</v>
+      </c>
+      <c r="V169" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W169" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>163324</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>535</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>4830</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>2955</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG169"/>
+  <dimension ref="A1:AG170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17892,6 +17892,109 @@
       </c>
       <c r="AG169" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1696</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1561020</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F170" t="n">
+        <v>12414</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>25552</v>
+      </c>
+      <c r="I170" t="n">
+        <v>15</v>
+      </c>
+      <c r="J170" t="n">
+        <v>51242</v>
+      </c>
+      <c r="K170" t="n">
+        <v>9</v>
+      </c>
+      <c r="L170" t="n">
+        <v>2217</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
+        <v>1708</v>
+      </c>
+      <c r="O170" t="n">
+        <v>1</v>
+      </c>
+      <c r="P170" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>6</v>
+      </c>
+      <c r="R170" t="n">
+        <v>356</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>565590</v>
+      </c>
+      <c r="U170" t="n">
+        <v>693</v>
+      </c>
+      <c r="V170" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W170" t="n">
+        <v>0</v>
+      </c>
+      <c r="X170" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>163554</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>230</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>4833</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>2958</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG170"/>
+  <dimension ref="A1:AG171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17995,6 +17995,109 @@
       </c>
       <c r="AG170" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1697</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1562970</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F171" t="n">
+        <v>12415</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>25554</v>
+      </c>
+      <c r="I171" t="n">
+        <v>2</v>
+      </c>
+      <c r="J171" t="n">
+        <v>51266</v>
+      </c>
+      <c r="K171" t="n">
+        <v>24</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2221</v>
+      </c>
+      <c r="M171" t="n">
+        <v>4</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1710</v>
+      </c>
+      <c r="O171" t="n">
+        <v>2</v>
+      </c>
+      <c r="P171" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>356</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>566986</v>
+      </c>
+      <c r="U171" t="n">
+        <v>1396</v>
+      </c>
+      <c r="V171" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W171" t="n">
+        <v>0</v>
+      </c>
+      <c r="X171" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>163883</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>329</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>4835</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>2962</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG171"/>
+  <dimension ref="A1:AG172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18098,6 +18098,109 @@
       </c>
       <c r="AG171" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1698</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1565060</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2090</v>
+      </c>
+      <c r="F172" t="n">
+        <v>12416</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>25561</v>
+      </c>
+      <c r="I172" t="n">
+        <v>7</v>
+      </c>
+      <c r="J172" t="n">
+        <v>51293</v>
+      </c>
+      <c r="K172" t="n">
+        <v>27</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2224</v>
+      </c>
+      <c r="M172" t="n">
+        <v>3</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1711</v>
+      </c>
+      <c r="O172" t="n">
+        <v>1</v>
+      </c>
+      <c r="P172" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
+        <v>356</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
+        <v>568358</v>
+      </c>
+      <c r="U172" t="n">
+        <v>1372</v>
+      </c>
+      <c r="V172" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W172" t="n">
+        <v>0</v>
+      </c>
+      <c r="X172" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>164246</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>4835</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>2968</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG172"/>
+  <dimension ref="A1:AG173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18200,6 +18200,109 @@
         <v>2968</v>
       </c>
       <c r="AG172" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1699</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1567160</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F173" t="n">
+        <v>12416</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>25565</v>
+      </c>
+      <c r="I173" t="n">
+        <v>4</v>
+      </c>
+      <c r="J173" t="n">
+        <v>51317</v>
+      </c>
+      <c r="K173" t="n">
+        <v>24</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2224</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1714</v>
+      </c>
+      <c r="O173" t="n">
+        <v>3</v>
+      </c>
+      <c r="P173" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>356</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>569994</v>
+      </c>
+      <c r="U173" t="n">
+        <v>1636</v>
+      </c>
+      <c r="V173" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W173" t="n">
+        <v>0</v>
+      </c>
+      <c r="X173" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>164578</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>332</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>4838</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>2974</v>
+      </c>
+      <c r="AG173" t="n">
         <v>6</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG173"/>
+  <dimension ref="A1:AG174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18304,6 +18304,109 @@
       </c>
       <c r="AG173" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1568720</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F174" t="n">
+        <v>12425</v>
+      </c>
+      <c r="G174" t="n">
+        <v>9</v>
+      </c>
+      <c r="H174" t="n">
+        <v>25570</v>
+      </c>
+      <c r="I174" t="n">
+        <v>5</v>
+      </c>
+      <c r="J174" t="n">
+        <v>51359</v>
+      </c>
+      <c r="K174" t="n">
+        <v>42</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2227</v>
+      </c>
+      <c r="M174" t="n">
+        <v>3</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1714</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>356</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>571572</v>
+      </c>
+      <c r="U174" t="n">
+        <v>1578</v>
+      </c>
+      <c r="V174" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W174" t="n">
+        <v>0</v>
+      </c>
+      <c r="X174" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>164871</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>293</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>4842</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>2986</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG174"/>
+  <dimension ref="A1:AG175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18407,6 +18407,109 @@
       </c>
       <c r="AG174" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1701</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1570540</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F175" t="n">
+        <v>12436</v>
+      </c>
+      <c r="G175" t="n">
+        <v>11</v>
+      </c>
+      <c r="H175" t="n">
+        <v>25586</v>
+      </c>
+      <c r="I175" t="n">
+        <v>16</v>
+      </c>
+      <c r="J175" t="n">
+        <v>51403</v>
+      </c>
+      <c r="K175" t="n">
+        <v>44</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2228</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>1716</v>
+      </c>
+      <c r="O175" t="n">
+        <v>2</v>
+      </c>
+      <c r="P175" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="n">
+        <v>356</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>573392</v>
+      </c>
+      <c r="U175" t="n">
+        <v>1820</v>
+      </c>
+      <c r="V175" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W175" t="n">
+        <v>0</v>
+      </c>
+      <c r="X175" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>165278</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>407</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>4844</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>2990</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG175"/>
+  <dimension ref="A1:AG176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18510,6 +18510,109 @@
       </c>
       <c r="AG175" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1702</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1572790</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F176" t="n">
+        <v>12439</v>
+      </c>
+      <c r="G176" t="n">
+        <v>3</v>
+      </c>
+      <c r="H176" t="n">
+        <v>25594</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>51447</v>
+      </c>
+      <c r="K176" t="n">
+        <v>44</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2229</v>
+      </c>
+      <c r="M176" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" t="n">
+        <v>1719</v>
+      </c>
+      <c r="O176" t="n">
+        <v>3</v>
+      </c>
+      <c r="P176" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
+        <v>356</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>575142</v>
+      </c>
+      <c r="U176" t="n">
+        <v>1750</v>
+      </c>
+      <c r="V176" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W176" t="n">
+        <v>0</v>
+      </c>
+      <c r="X176" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>165641</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>4846</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>2997</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG176"/>
+  <dimension ref="A1:AG177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18613,6 +18613,109 @@
       </c>
       <c r="AG176" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1703</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1574620</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1830</v>
+      </c>
+      <c r="F177" t="n">
+        <v>12439</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>25597</v>
+      </c>
+      <c r="I177" t="n">
+        <v>3</v>
+      </c>
+      <c r="J177" t="n">
+        <v>51501</v>
+      </c>
+      <c r="K177" t="n">
+        <v>54</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2230</v>
+      </c>
+      <c r="M177" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" t="n">
+        <v>1720</v>
+      </c>
+      <c r="O177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P177" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="n">
+        <v>356</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>577209</v>
+      </c>
+      <c r="U177" t="n">
+        <v>2067</v>
+      </c>
+      <c r="V177" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W177" t="n">
+        <v>0</v>
+      </c>
+      <c r="X177" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>166088</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>447</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>4851</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>3003</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG177"/>
+  <dimension ref="A1:AG178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18716,6 +18716,109 @@
       </c>
       <c r="AG177" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1704</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1576600</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F178" t="n">
+        <v>12444</v>
+      </c>
+      <c r="G178" t="n">
+        <v>5</v>
+      </c>
+      <c r="H178" t="n">
+        <v>25600</v>
+      </c>
+      <c r="I178" t="n">
+        <v>3</v>
+      </c>
+      <c r="J178" t="n">
+        <v>51565</v>
+      </c>
+      <c r="K178" t="n">
+        <v>64</v>
+      </c>
+      <c r="L178" t="n">
+        <v>2232</v>
+      </c>
+      <c r="M178" t="n">
+        <v>2</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1722</v>
+      </c>
+      <c r="O178" t="n">
+        <v>2</v>
+      </c>
+      <c r="P178" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>356</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>579064</v>
+      </c>
+      <c r="U178" t="n">
+        <v>1855</v>
+      </c>
+      <c r="V178" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W178" t="n">
+        <v>0</v>
+      </c>
+      <c r="X178" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>166501</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>413</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>4852</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>3011</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG178"/>
+  <dimension ref="A1:AG179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18819,6 +18819,109 @@
       </c>
       <c r="AG178" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1705</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1578450</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F179" t="n">
+        <v>12447</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="n">
+        <v>25605</v>
+      </c>
+      <c r="I179" t="n">
+        <v>5</v>
+      </c>
+      <c r="J179" t="n">
+        <v>51614</v>
+      </c>
+      <c r="K179" t="n">
+        <v>49</v>
+      </c>
+      <c r="L179" t="n">
+        <v>2237</v>
+      </c>
+      <c r="M179" t="n">
+        <v>5</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1725</v>
+      </c>
+      <c r="O179" t="n">
+        <v>3</v>
+      </c>
+      <c r="P179" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="n">
+        <v>356</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>580802</v>
+      </c>
+      <c r="U179" t="n">
+        <v>1738</v>
+      </c>
+      <c r="V179" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W179" t="n">
+        <v>0</v>
+      </c>
+      <c r="X179" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>166918</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>417</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>4856</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>3017</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG179"/>
+  <dimension ref="A1:AG180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18922,6 +18922,109 @@
       </c>
       <c r="AG179" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1706</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1580440</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F180" t="n">
+        <v>12448</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>25609</v>
+      </c>
+      <c r="I180" t="n">
+        <v>4</v>
+      </c>
+      <c r="J180" t="n">
+        <v>51632</v>
+      </c>
+      <c r="K180" t="n">
+        <v>18</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2239</v>
+      </c>
+      <c r="M180" t="n">
+        <v>2</v>
+      </c>
+      <c r="N180" t="n">
+        <v>1726</v>
+      </c>
+      <c r="O180" t="n">
+        <v>1</v>
+      </c>
+      <c r="P180" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>356</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>582458</v>
+      </c>
+      <c r="U180" t="n">
+        <v>1656</v>
+      </c>
+      <c r="V180" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W180" t="n">
+        <v>0</v>
+      </c>
+      <c r="X180" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>167240</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>322</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>4858</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>3018</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG180"/>
+  <dimension ref="A1:AG181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19025,6 +19025,109 @@
       </c>
       <c r="AG180" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1707</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1581840</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F181" t="n">
+        <v>12448</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>25609</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>51653</v>
+      </c>
+      <c r="K181" t="n">
+        <v>21</v>
+      </c>
+      <c r="L181" t="n">
+        <v>2241</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1727</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>356</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>584252</v>
+      </c>
+      <c r="U181" t="n">
+        <v>1794</v>
+      </c>
+      <c r="V181" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W181" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>167472</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>232</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>4859</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3025</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG181"/>
+  <dimension ref="A1:AG182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19127,6 +19127,109 @@
         <v>3025</v>
       </c>
       <c r="AG181" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1708</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1583350</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1510</v>
+      </c>
+      <c r="F182" t="n">
+        <v>12448</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>25609</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>51674</v>
+      </c>
+      <c r="K182" t="n">
+        <v>21</v>
+      </c>
+      <c r="L182" t="n">
+        <v>2241</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1727</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>356</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>585795</v>
+      </c>
+      <c r="U182" t="n">
+        <v>1543</v>
+      </c>
+      <c r="V182" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W182" t="n">
+        <v>0</v>
+      </c>
+      <c r="X182" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>167738</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>266</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>4859</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>3032</v>
+      </c>
+      <c r="AG182" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG182"/>
+  <dimension ref="A1:AG183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19231,6 +19231,109 @@
       </c>
       <c r="AG182" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1709</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1584910</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F183" t="n">
+        <v>12449</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>25614</v>
+      </c>
+      <c r="I183" t="n">
+        <v>5</v>
+      </c>
+      <c r="J183" t="n">
+        <v>51699</v>
+      </c>
+      <c r="K183" t="n">
+        <v>25</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2245</v>
+      </c>
+      <c r="M183" t="n">
+        <v>4</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1727</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>1</v>
+      </c>
+      <c r="R183" t="n">
+        <v>356</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>587409</v>
+      </c>
+      <c r="U183" t="n">
+        <v>1614</v>
+      </c>
+      <c r="V183" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W183" t="n">
+        <v>0</v>
+      </c>
+      <c r="X183" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>168010</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>272</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>4860</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>3036</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG183"/>
+  <dimension ref="A1:AG184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19334,6 +19334,109 @@
       </c>
       <c r="AG183" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1710</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1586500</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F184" t="n">
+        <v>12450</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>25617</v>
+      </c>
+      <c r="I184" t="n">
+        <v>3</v>
+      </c>
+      <c r="J184" t="n">
+        <v>51720</v>
+      </c>
+      <c r="K184" t="n">
+        <v>21</v>
+      </c>
+      <c r="L184" t="n">
+        <v>2246</v>
+      </c>
+      <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
+        <v>1728</v>
+      </c>
+      <c r="O184" t="n">
+        <v>1</v>
+      </c>
+      <c r="P184" t="n">
+        <v>452</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>2</v>
+      </c>
+      <c r="R184" t="n">
+        <v>356</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>588998</v>
+      </c>
+      <c r="U184" t="n">
+        <v>1589</v>
+      </c>
+      <c r="V184" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W184" t="n">
+        <v>0</v>
+      </c>
+      <c r="X184" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>168274</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>264</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>4860</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>3039</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG184"/>
+  <dimension ref="A1:AG185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19437,6 +19437,109 @@
       </c>
       <c r="AG184" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1711</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1588170</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F185" t="n">
+        <v>12450</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>25620</v>
+      </c>
+      <c r="I185" t="n">
+        <v>3</v>
+      </c>
+      <c r="J185" t="n">
+        <v>51739</v>
+      </c>
+      <c r="K185" t="n">
+        <v>19</v>
+      </c>
+      <c r="L185" t="n">
+        <v>2247</v>
+      </c>
+      <c r="M185" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" t="n">
+        <v>1730</v>
+      </c>
+      <c r="O185" t="n">
+        <v>2</v>
+      </c>
+      <c r="P185" t="n">
+        <v>452</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>356</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>590661</v>
+      </c>
+      <c r="U185" t="n">
+        <v>1663</v>
+      </c>
+      <c r="V185" t="n">
+        <v>5126</v>
+      </c>
+      <c r="W185" t="n">
+        <v>0</v>
+      </c>
+      <c r="X185" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>168480</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>206</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>4860</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>3045</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
